--- a/01_Yetkisiz_Kullanıcı_Başlangıç_ve_Header/1 - UA - SPHD.xlsx
+++ b/01_Yetkisiz_Kullanıcı_Başlangıç_ve_Header/1 - UA - SPHD.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bovay\Desktop\¨¨¨¨¨¨\PROJECTS\CV TASLAK\POWER PULSE - PROJE\PLANLAMA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bovay\Desktop\¨¨¨¨¨¨\PROJECTS\CV TASLAK\POWER PULSE - PROJE\PLANLAMA\01 - YETKİSİZ KULLANICI - BAŞLANGIÇ VE HEADER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD63BD63-44ED-47F4-9EA1-5BF0CD402A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA64A37F-3941-46A4-8F69-C8BCB05D1648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="1. GEREKSİNİM TAKİP MATRİKSİ" sheetId="10" r:id="rId1"/>
+    <sheet name="1. GEREKSİNİM TAKİP MATRİSİ" sheetId="10" r:id="rId1"/>
     <sheet name="1.1. ŞABLON GENİŞLİĞİ UYUMU" sheetId="2" r:id="rId2"/>
     <sheet name="1.1.1. BUG RAPORU" sheetId="6" r:id="rId3"/>
     <sheet name="1.1.2. BUG RAPORU" sheetId="8" r:id="rId4"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="219">
   <si>
     <r>
       <rPr>
@@ -316,54 +316,7 @@
     <t>Test Envarement:</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="162"/>
-      </rPr>
-      <t>Date:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="162"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Envirement:</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="162"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Date:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
   </si>
   <si>
     <t>Test Envirement:</t>
@@ -620,9 +573,6 @@
     <t xml:space="preserve">Windows 11 Home Single Language, Masaüstü (MS), Chrome Sürüm 141.0.7390.122 </t>
   </si>
   <si>
-    <t>Başlangıç sayfasında sağ altta küçük turuncu dikdörtgenin içindeki kalori değerini ifade etmesi gereken sayı çok büyük</t>
-  </si>
-  <si>
     <t>Başlangıç sayfasında sağ altta küçük turuncu dikdörtgenin içindeki kalori değerini ifade etmesi gereken sayı yanlış</t>
   </si>
   <si>
@@ -666,9 +616,6 @@
   </si>
   <si>
     <t>Bug ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kullanıcıların gerçekleştirdiği egzersiz sayısı, egzersiz için harcadıkları saat, uygulamaya kayıtlı toplam kullanıcı sayısı görünmemektedir. </t>
   </si>
   <si>
     <t xml:space="preserve">Kullanıcıların egzersiz sayısı, saati, toplam kayıtlı kullanıcı sayısı başlangıç sayfasında görünmmektedir. </t>
@@ -839,9 +786,6 @@
     <t>Priority</t>
   </si>
   <si>
-    <t>Test Type</t>
-  </si>
-  <si>
     <t>Checklist ID</t>
   </si>
   <si>
@@ -851,9 +795,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t>Document Title:</t>
   </si>
   <si>
@@ -866,9 +807,6 @@
     <t>Module Code:</t>
   </si>
   <si>
-    <t>1. Gereksinim Takip Matriksi</t>
-  </si>
-  <si>
     <t>Yetkisiz Kullanıcı – Başlangıç Sayfası ve Header</t>
   </si>
   <si>
@@ -944,24 +882,6 @@
     <t>Logo tıklandığında kullanıcı başlangıç sayfasına yönlendirilmelidir.</t>
   </si>
   <si>
-    <t>Navigation</t>
-  </si>
-  <si>
-    <t>UI</t>
-  </si>
-  <si>
-    <t>Responsive</t>
-  </si>
-  <si>
-    <t>Mobile UI</t>
-  </si>
-  <si>
-    <t>Tablet UI</t>
-  </si>
-  <si>
-    <t>Desktop UI</t>
-  </si>
-  <si>
     <t>Passed</t>
   </si>
   <si>
@@ -992,9 +912,6 @@
     <t>CL-003 [UA-SP]</t>
   </si>
   <si>
-    <t>Video egzersizi sayısı görüntülenmelidir.</t>
-  </si>
-  <si>
     <t>Kullanıcılar tarafından yakılan toplam kalori görüntülenmelidir.</t>
   </si>
   <si>
@@ -1010,19 +927,160 @@
     <t>CL-004 [UA-SP]</t>
   </si>
   <si>
-    <t>Statistics</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="162"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Date:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="162"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>16.07.2026</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Date:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="162"/>
+      </rPr>
+      <t xml:space="preserve"> 16.07.2026</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Date:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="162"/>
+      </rPr>
+      <t xml:space="preserve"> 17.07.2026</t>
+    </r>
+  </si>
+  <si>
+    <t>Document Type</t>
+  </si>
+  <si>
+    <t>Responsive / Functional</t>
+  </si>
+  <si>
+    <t>Mobile UI / Functional</t>
+  </si>
+  <si>
+    <t>Tablet UI / Functional</t>
+  </si>
+  <si>
+    <t>Desktop UI / Functional</t>
+  </si>
+  <si>
+    <t>UI / Functional</t>
+  </si>
+  <si>
+    <t>Navigation / Functional</t>
+  </si>
+  <si>
+    <t>Statistics / Functional</t>
+  </si>
+  <si>
+    <t>Video egzersizi toplam sayısı görüntülenmelidir.</t>
+  </si>
+  <si>
+    <t>Feature / Test Type</t>
+  </si>
+  <si>
+    <t>Başlangıç sayfasında sağ altta küçük turuncu dikdörtgenin içinde görüntülenen değer (kalori değeri) diğer ekran görünümlerindeki değerlerle tutarsız büyüklükte</t>
+  </si>
+  <si>
+    <t>Başlangıç sayfasında görüntülenmesi gereken bazı istatistik bilgileri ve bunlara ait görseller bulunmamaktadır.</t>
+  </si>
+  <si>
+    <t>1. Gereksinim Takip Matrisi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1315,20 +1373,20 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1338,10 +1396,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1349,208 +1407,211 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="4" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="4" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Çıkış" xfId="1" builtinId="21"/>
@@ -2124,760 +2185,760 @@
   <cols>
     <col min="1" max="1" width="21.6328125" style="42" customWidth="1"/>
     <col min="2" max="2" width="11.54296875" style="42" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="42" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" style="42" customWidth="1"/>
     <col min="4" max="4" width="19.1796875" style="42" customWidth="1"/>
     <col min="5" max="5" width="16.453125" style="42" customWidth="1"/>
     <col min="6" max="6" width="15.1796875" style="42" customWidth="1"/>
     <col min="7" max="7" width="16.90625" style="42" customWidth="1"/>
-    <col min="8" max="8" width="21.453125" style="42" customWidth="1"/>
+    <col min="8" max="8" width="23.08984375" style="42" customWidth="1"/>
     <col min="9" max="16384" width="8.7265625" style="42"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="47" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="48"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="47" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" s="60" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="F2" s="49">
+        <v>46220</v>
+      </c>
+      <c r="G2" s="48"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="47" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="43" t="s">
         <v>169</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="90" t="s">
+      <c r="F3" s="44" t="s">
+        <v>168</v>
+      </c>
+      <c r="G3" s="48"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="47" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+    </row>
+    <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="45" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>206</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>158</v>
+      </c>
+      <c r="G6" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="H6" s="57" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="45.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D7" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="E7" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F7" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G7" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H7" s="53" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="E8" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F8" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="G8" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="H8" s="53" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="F1" s="92" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="92"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="91" t="s">
-        <v>166</v>
-      </c>
-      <c r="B2" s="89" t="s">
-        <v>172</v>
-      </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="90" t="s">
+      <c r="B9" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="E9" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F9" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G9" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H9" s="53" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F2" s="93">
-        <v>46220</v>
-      </c>
-      <c r="G2" s="92"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="91" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3" s="89" t="s">
-        <v>170</v>
-      </c>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="43" t="s">
+      <c r="B10" s="53" t="s">
         <v>176</v>
       </c>
-      <c r="F3" s="44" t="s">
+      <c r="C10" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="E10" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F10" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="G10" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="H10" s="53" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="52" t="s">
         <v>175</v>
       </c>
-      <c r="G3" s="92"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
-        <v>168</v>
-      </c>
-      <c r="B4" s="89" t="s">
-        <v>171</v>
-      </c>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="92"/>
-      <c r="G4" s="92"/>
-    </row>
-    <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="88" t="s">
+      <c r="B11" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" s="55" t="s">
         <v>177</v>
       </c>
-      <c r="B6" s="88" t="s">
-        <v>159</v>
-      </c>
-      <c r="C6" s="88" t="s">
-        <v>160</v>
-      </c>
-      <c r="D6" s="88" t="s">
-        <v>161</v>
-      </c>
-      <c r="E6" s="88" t="s">
-        <v>162</v>
-      </c>
-      <c r="F6" s="88" t="s">
-        <v>163</v>
-      </c>
-      <c r="G6" s="88" t="s">
-        <v>129</v>
-      </c>
-      <c r="H6" s="97" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="45.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="95" t="s">
+      <c r="D11" s="53" t="s">
         <v>178</v>
       </c>
-      <c r="B7" s="97" t="s">
+      <c r="E11" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F11" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="G11" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="H11" s="53" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="53" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="B12" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C12" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D12" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="E12" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G12" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H12" s="53" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="51.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="58" t="s">
+        <v>181</v>
+      </c>
+      <c r="B13" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C13" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="E13" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F13" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G13" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H13" s="53" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="B14" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D14" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="E14" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F14" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G14" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H14" s="53" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="58" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="99" t="s">
+      <c r="B15" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D15" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F15" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G15" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H15" s="53" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="58" t="s">
         <v>184</v>
       </c>
-      <c r="D7" s="97" t="s">
+      <c r="B16" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C16" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D16" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="E16" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F16" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G16" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H16" s="53" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="59.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="58" t="s">
         <v>185</v>
       </c>
-      <c r="E7" s="101" t="s">
+      <c r="B17" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D17" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="E17" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F17" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G17" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H17" s="53" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="58" t="s">
         <v>186</v>
       </c>
-      <c r="F7" s="97" t="s">
+      <c r="B18" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C18" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D18" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F18" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G18" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H18" s="53" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="59.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="B19" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="E19" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F19" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G19" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H19" s="53" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="58" t="s">
+        <v>190</v>
+      </c>
+      <c r="B20" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="E20" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F20" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G20" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H20" s="53" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="69" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="58" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="E21" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F21" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G21" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H21" s="53" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="B22" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C22" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D22" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="E22" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G22" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H22" s="53" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="66.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="58" t="s">
+        <v>193</v>
+      </c>
+      <c r="B23" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C23" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="E23" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F23" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G23" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H23" s="53" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="B24" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C24" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="E24" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F24" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G24" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H24" s="53" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="B25" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C25" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="E25" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F25" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G25" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H25" s="53" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="58" t="s">
+        <v>196</v>
+      </c>
+      <c r="B26" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C26" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="E26" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F26" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G26" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H26" s="53" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="76" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="B27" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C27" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>202</v>
+      </c>
+      <c r="E27" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F27" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G27" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H27" s="53" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="58" t="s">
+        <v>198</v>
+      </c>
+      <c r="B28" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C28" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>202</v>
+      </c>
+      <c r="E28" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F28" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G28" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H28" s="53" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="82" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="B29" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C29" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>202</v>
+      </c>
+      <c r="E29" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F29" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="G29" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="H29" s="53" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="B30" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C30" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>202</v>
+      </c>
+      <c r="E30" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="G30" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="H30" s="53" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="78.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="58" t="s">
         <v>201</v>
       </c>
-      <c r="G7" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H7" s="97" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="95" t="s">
+      <c r="B31" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C31" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>202</v>
+      </c>
+      <c r="E31" s="57" t="s">
         <v>179</v>
       </c>
-      <c r="B8" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C8" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D8" s="97" t="s">
-        <v>185</v>
-      </c>
-      <c r="E8" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F8" s="97" t="s">
-        <v>202</v>
-      </c>
-      <c r="G8" s="97" t="s">
-        <v>148</v>
-      </c>
-      <c r="H8" s="97" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="95" t="s">
-        <v>180</v>
-      </c>
-      <c r="B9" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C9" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="97" t="s">
-        <v>185</v>
-      </c>
-      <c r="E9" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F9" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G9" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H9" s="97" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="95" t="s">
-        <v>181</v>
-      </c>
-      <c r="B10" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C10" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D10" s="97" t="s">
-        <v>185</v>
-      </c>
-      <c r="E10" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F10" s="103" t="s">
-        <v>202</v>
-      </c>
-      <c r="G10" s="97" t="s">
-        <v>149</v>
-      </c>
-      <c r="H10" s="97" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="96" t="s">
-        <v>182</v>
-      </c>
-      <c r="B11" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C11" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D11" s="97" t="s">
-        <v>185</v>
-      </c>
-      <c r="E11" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F11" s="103" t="s">
-        <v>202</v>
-      </c>
-      <c r="G11" s="97" t="s">
-        <v>150</v>
-      </c>
-      <c r="H11" s="97" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="53" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94" t="s">
-        <v>187</v>
-      </c>
-      <c r="B12" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C12" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D12" s="97" t="s">
+      <c r="F31" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="G31" s="53" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F12" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G12" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H12" s="97" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="51.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="102" t="s">
-        <v>188</v>
-      </c>
-      <c r="B13" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C13" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D13" s="97" t="s">
-        <v>151</v>
-      </c>
-      <c r="E13" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F13" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G13" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H13" s="97" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="102" t="s">
-        <v>189</v>
-      </c>
-      <c r="B14" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C14" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D14" s="97" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F14" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G14" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H14" s="97" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="102" t="s">
-        <v>190</v>
-      </c>
-      <c r="B15" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C15" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D15" s="97" t="s">
-        <v>151</v>
-      </c>
-      <c r="E15" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F15" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G15" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H15" s="97" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="102" t="s">
-        <v>191</v>
-      </c>
-      <c r="B16" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C16" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D16" s="97" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F16" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G16" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H16" s="97" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="59.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102" t="s">
-        <v>192</v>
-      </c>
-      <c r="B17" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C17" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D17" s="97" t="s">
-        <v>151</v>
-      </c>
-      <c r="E17" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F17" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G17" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H17" s="97" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="102" t="s">
-        <v>193</v>
-      </c>
-      <c r="B18" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C18" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D18" s="97" t="s">
-        <v>151</v>
-      </c>
-      <c r="E18" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F18" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G18" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H18" s="97" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="59.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="102" t="s">
-        <v>194</v>
-      </c>
-      <c r="B19" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C19" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D19" s="97" t="s">
-        <v>151</v>
-      </c>
-      <c r="E19" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F19" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G19" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H19" s="97" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="102" t="s">
-        <v>203</v>
-      </c>
-      <c r="B20" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C20" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D20" s="97" t="s">
-        <v>210</v>
-      </c>
-      <c r="E20" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F20" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G20" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H20" s="97" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="69" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="102" t="s">
-        <v>204</v>
-      </c>
-      <c r="B21" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C21" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D21" s="97" t="s">
-        <v>210</v>
-      </c>
-      <c r="E21" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F21" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G21" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H21" s="97" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="102" t="s">
-        <v>205</v>
-      </c>
-      <c r="B22" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C22" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D22" s="97" t="s">
-        <v>210</v>
-      </c>
-      <c r="E22" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F22" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G22" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H22" s="97" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="66.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="102" t="s">
-        <v>206</v>
-      </c>
-      <c r="B23" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C23" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D23" s="97" t="s">
-        <v>210</v>
-      </c>
-      <c r="E23" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F23" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G23" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H23" s="97" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="102" t="s">
-        <v>207</v>
-      </c>
-      <c r="B24" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C24" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D24" s="97" t="s">
-        <v>210</v>
-      </c>
-      <c r="E24" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F24" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G24" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H24" s="97" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="102" t="s">
-        <v>208</v>
-      </c>
-      <c r="B25" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C25" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D25" s="97" t="s">
-        <v>210</v>
-      </c>
-      <c r="E25" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F25" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G25" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H25" s="97" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="102" t="s">
-        <v>209</v>
-      </c>
-      <c r="B26" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C26" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D26" s="97" t="s">
-        <v>210</v>
-      </c>
-      <c r="E26" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F26" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G26" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H26" s="97" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="76" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="102" t="s">
-        <v>211</v>
-      </c>
-      <c r="B27" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C27" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D27" s="97" t="s">
-        <v>216</v>
-      </c>
-      <c r="E27" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F27" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G27" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H27" s="97" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="102" t="s">
-        <v>212</v>
-      </c>
-      <c r="B28" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C28" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D28" s="97" t="s">
-        <v>216</v>
-      </c>
-      <c r="E28" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F28" s="97" t="s">
-        <v>201</v>
-      </c>
-      <c r="G28" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="H28" s="97" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="82" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="102" t="s">
+      <c r="H31" s="53" t="s">
         <v>213</v>
       </c>
-      <c r="B29" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C29" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D29" s="97" t="s">
-        <v>216</v>
-      </c>
-      <c r="E29" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F29" s="97" t="s">
-        <v>202</v>
-      </c>
-      <c r="G29" s="97" t="s">
-        <v>155</v>
-      </c>
-      <c r="H29" s="97" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="102" t="s">
-        <v>214</v>
-      </c>
-      <c r="B30" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C30" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D30" s="97" t="s">
-        <v>216</v>
-      </c>
-      <c r="E30" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F30" s="97" t="s">
-        <v>202</v>
-      </c>
-      <c r="G30" s="97" t="s">
-        <v>155</v>
-      </c>
-      <c r="H30" s="97" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="78.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="102" t="s">
-        <v>215</v>
-      </c>
-      <c r="B31" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C31" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="D31" s="97" t="s">
-        <v>216</v>
-      </c>
-      <c r="E31" s="101" t="s">
-        <v>186</v>
-      </c>
-      <c r="F31" s="97" t="s">
-        <v>202</v>
-      </c>
-      <c r="G31" s="97" t="s">
-        <v>155</v>
-      </c>
-      <c r="H31" s="97" t="s">
-        <v>217</v>
-      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="H32" s="98"/>
+      <c r="H32" s="54"/>
     </row>
     <row r="33" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H33" s="98"/>
+      <c r="H33" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2904,13 +2965,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="100" t="s">
-        <v>147</v>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="56" t="s">
+        <v>143</v>
       </c>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
@@ -2924,10 +2985,10 @@
       <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="55" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="56"/>
+      <c r="A3" s="68" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" s="69"/>
       <c r="D3" s="7" t="s">
         <v>0</v>
       </c>
@@ -2942,68 +3003,68 @@
       <c r="F4" s="10"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="65" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="65"/>
+      <c r="C5" s="66" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="65" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="65"/>
+      <c r="C6" s="66" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="47" t="s">
+      <c r="B7" s="65"/>
+      <c r="C7" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="47" t="s">
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="48" t="s">
+      <c r="B8" s="65"/>
+      <c r="C8" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
       <c r="F8" s="11"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="52"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="64"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="54" t="s">
+      <c r="B11" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="54"/>
+      <c r="C11" s="67"/>
       <c r="D11" s="30" t="s">
         <v>3</v>
       </c>
@@ -3011,97 +3072,97 @@
         <v>4</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="45" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="45"/>
+      <c r="B12" s="70" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="70"/>
       <c r="D12" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="32" t="s">
         <v>69</v>
-      </c>
-      <c r="E12" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="32" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="45"/>
+      <c r="C13" s="70"/>
       <c r="D13" s="31" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="46"/>
+      <c r="B14" s="71" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="71"/>
       <c r="D14" s="31" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F14" s="32" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="46" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="46"/>
+      <c r="B15" s="71" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="71"/>
       <c r="D15" s="34" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="46"/>
+      <c r="C16" s="71"/>
       <c r="D16" s="34" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -3122,6 +3183,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A7:B7"/>
@@ -3132,13 +3200,6 @@
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:E6"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3161,7 +3222,7 @@
         <v>50</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
@@ -3179,7 +3240,7 @@
       </c>
       <c r="D2" s="28"/>
       <c r="E2" s="28" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3193,253 +3254,241 @@
         <v>40</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="57" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
+      <c r="B4" s="73" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="57" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
+      <c r="B5" s="73" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
+      <c r="B6" s="73" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="58"/>
-      <c r="B7" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
+      <c r="A7" s="74"/>
+      <c r="B7" s="73" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="28">
         <v>1</v>
       </c>
-      <c r="B9" s="57" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
+      <c r="B9" s="73" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="73"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="28">
         <v>2</v>
       </c>
-      <c r="B10" s="57" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
+      <c r="B10" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="58" t="s">
+      <c r="A11" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="28">
         <v>1</v>
       </c>
-      <c r="B12" s="57" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
+      <c r="B12" s="73" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="28">
         <v>2</v>
       </c>
-      <c r="B13" s="57" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
+      <c r="B13" s="73" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="28">
         <v>3</v>
       </c>
-      <c r="B14" s="57" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
+      <c r="B14" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="28">
         <v>4</v>
       </c>
-      <c r="B15" s="57" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
+      <c r="B15" s="73" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="74"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="28">
         <v>5</v>
       </c>
-      <c r="B16" s="57" t="s">
+      <c r="B16" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="74" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="74"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+    </row>
+    <row r="18" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="75" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" s="76"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="77"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="73" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="74"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="73" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="58" t="s">
-        <v>89</v>
-      </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-    </row>
-    <row r="18" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="60" t="s">
-        <v>121</v>
-      </c>
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="62"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="57" t="s">
+      <c r="B20" s="74"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="57" t="s">
+      <c r="B21" s="74"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="74"/>
+    </row>
+    <row r="22" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="75" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" s="76"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="77"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="73" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="58" t="s">
+      <c r="B23" s="74"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="73" t="s">
         <v>93</v>
       </c>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-    </row>
-    <row r="22" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="60" t="s">
-        <v>122</v>
-      </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="62"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="B23" s="58"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="57" t="s">
-        <v>95</v>
-      </c>
-      <c r="B24" s="58"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
     </row>
     <row r="25" spans="1:5" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="74"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="58" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
+      <c r="A26" s="74" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="74"/>
+      <c r="C26" s="74"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
@@ -3452,6 +3501,18 @@
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A21:E21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3476,7 +3537,7 @@
         <v>50</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
@@ -3494,7 +3555,7 @@
       </c>
       <c r="D2" s="28"/>
       <c r="E2" s="28" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3508,135 +3569,135 @@
         <v>40</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="57" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
+      <c r="B4" s="73" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="57" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
+      <c r="B5" s="73" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="57" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
+      <c r="B6" s="73" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="58"/>
-      <c r="B7" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
+      <c r="A7" s="74"/>
+      <c r="B7" s="73" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="28">
         <v>1</v>
       </c>
-      <c r="B9" s="57" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
+      <c r="B9" s="73" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="73"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="28">
         <v>2</v>
       </c>
-      <c r="B10" s="57" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
+      <c r="B10" s="73" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="58" t="s">
+      <c r="A11" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="28">
         <v>1</v>
       </c>
-      <c r="B12" s="57" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
+      <c r="B12" s="73" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="28">
         <v>2</v>
       </c>
-      <c r="B13" s="57" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
+      <c r="B13" s="73" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="28">
         <v>3</v>
       </c>
-      <c r="B14" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
+      <c r="B14" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="28">
         <v>4</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="28">
@@ -3644,100 +3705,100 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="58" t="s">
-        <v>89</v>
-      </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
+      <c r="A17" s="74" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="74"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="57" t="s">
+      <c r="A18" s="73" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="74"/>
+      <c r="C18" s="74"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="73" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="74"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="74" t="s">
         <v>106</v>
       </c>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="57" t="s">
+      <c r="B20" s="74"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="73" t="s">
         <v>92</v>
       </c>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="58" t="s">
-        <v>108</v>
-      </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="74"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="57" t="s">
-        <v>95</v>
-      </c>
-      <c r="B22" s="58"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
+      <c r="A22" s="73" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="74"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
     </row>
     <row r="23" spans="1:5" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="58"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="58" t="s">
-        <v>109</v>
-      </c>
-      <c r="B24" s="58"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
+      <c r="A24" s="74" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="74"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B13:E13"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B15:E15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3762,7 +3823,7 @@
         <v>50</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
@@ -3780,7 +3841,7 @@
       </c>
       <c r="D2" s="28"/>
       <c r="E2" s="28" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3794,229 +3855,219 @@
         <v>40</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
+      <c r="B4" s="73" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="57" t="s">
-        <v>114</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
+      <c r="B5" s="73" t="s">
+        <v>216</v>
+      </c>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="57" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
+      <c r="B6" s="73" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="58"/>
-      <c r="B7" s="57" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
+      <c r="A7" s="74"/>
+      <c r="B7" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="28">
         <v>1</v>
       </c>
-      <c r="B9" s="57" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
+      <c r="B9" s="73" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="73"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="28">
         <v>2</v>
       </c>
-      <c r="B10" s="57" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
+      <c r="B10" s="73" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="58" t="s">
+      <c r="A11" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="28">
         <v>1</v>
       </c>
-      <c r="B12" s="57" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
+      <c r="B12" s="73" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="28">
         <v>2</v>
       </c>
-      <c r="B13" s="57" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
+      <c r="B13" s="73" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="28">
         <v>3</v>
       </c>
-      <c r="B14" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
+      <c r="B14" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="28">
         <v>4</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="28">
         <v>5</v>
       </c>
-      <c r="B16" s="63"/>
-      <c r="C16" s="64"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="65"/>
+      <c r="B16" s="79"/>
+      <c r="C16" s="80"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="81"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="58" t="s">
-        <v>111</v>
-      </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
+      <c r="A17" s="74" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="74"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="57" t="s">
+      <c r="A18" s="73" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="74"/>
+      <c r="C18" s="74"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="73" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="74"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="74"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="73" t="s">
+        <v>116</v>
+      </c>
+      <c r="B21" s="74"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="74"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="73" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="58" t="s">
-        <v>112</v>
-      </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="57" t="s">
-        <v>119</v>
-      </c>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="57" t="s">
-        <v>120</v>
-      </c>
-      <c r="B22" s="58"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
     </row>
     <row r="23" spans="1:5" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="58"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="58" t="s">
-        <v>109</v>
-      </c>
-      <c r="B24" s="58"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
+      <c r="A24" s="74" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="74"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
@@ -4029,6 +4080,16 @@
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A21:E21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4047,16 +4108,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="49"/>
+      <c r="B1" s="61"/>
       <c r="C1" s="8"/>
       <c r="D1" s="25" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="26" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -4067,10 +4128,10 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="55" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="56"/>
+      <c r="A3" s="83" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" s="69"/>
       <c r="D3" s="24" t="s">
         <v>56</v>
       </c>
@@ -4085,63 +4146,63 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="66" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
+      <c r="A5" s="82" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="82"/>
+      <c r="C5" s="66" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="53" t="s">
-        <v>146</v>
-      </c>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
+      <c r="A6" s="82" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="82"/>
+      <c r="C6" s="66" t="s">
+        <v>142</v>
+      </c>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="66" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="66"/>
-      <c r="C7" s="48" t="s">
+      <c r="A7" s="82" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="82"/>
+      <c r="C7" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="66" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="66"/>
-      <c r="C8" s="48" t="s">
+      <c r="A8" s="82" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="82"/>
+      <c r="C8" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="67" t="s">
+      <c r="A10" s="84" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
+      <c r="B10" s="84"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -4149,21 +4210,21 @@
         <v>15</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -4171,21 +4232,21 @@
         <v>16</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -4193,10 +4254,10 @@
         <v>17</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -4204,25 +4265,25 @@
         <v>18</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:E8"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:E5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4240,16 +4301,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="85" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
       <c r="D1" s="23" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -4260,15 +4321,15 @@
       <c r="E2" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="77" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="77"/>
+      <c r="A3" s="88" t="s">
+        <v>204</v>
+      </c>
+      <c r="B3" s="88"/>
       <c r="C3" s="18"/>
-      <c r="D3" s="77" t="s">
+      <c r="D3" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="77"/>
+      <c r="E3" s="88"/>
     </row>
     <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="13"/>
@@ -4278,44 +4339,44 @@
       <c r="E4" s="13"/>
     </row>
     <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="76" t="s">
+      <c r="A5" s="86" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="86"/>
+      <c r="C5" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
     </row>
     <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="69" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="76" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
+      <c r="A6" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="86"/>
+      <c r="C6" s="87" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
     </row>
     <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="69" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="69"/>
-      <c r="C7" s="70" t="s">
+      <c r="A7" s="86" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="86"/>
+      <c r="C7" s="90" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="90"/>
     </row>
     <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="71"/>
-      <c r="B8" s="71"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
+      <c r="A8" s="91"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="89"/>
+      <c r="E8" s="89"/>
     </row>
     <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
@@ -4325,100 +4386,93 @@
       <c r="E9" s="14"/>
     </row>
     <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="72" t="s">
+      <c r="A10" s="92" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="92"/>
+      <c r="D10" s="92"/>
       <c r="E10" s="14"/>
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.4">
-      <c r="A11" s="73" t="s">
+      <c r="A11" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="73"/>
+      <c r="B11" s="93"/>
       <c r="C11" s="37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="73" t="s">
+      <c r="A12" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="73"/>
+      <c r="B12" s="93"/>
       <c r="C12" s="38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
     </row>
     <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="73"/>
+      <c r="B13" s="93"/>
       <c r="C13" s="38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
     </row>
     <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="74" t="s">
+      <c r="A14" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="74"/>
+      <c r="B14" s="94"/>
       <c r="C14" s="38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="68"/>
+      <c r="B15" s="89"/>
       <c r="C15" s="38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
     </row>
     <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="68" t="s">
+      <c r="A16" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="68"/>
+      <c r="B16" s="89"/>
       <c r="C16" s="38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
     </row>
     <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="68"/>
+      <c r="B17" s="89"/>
       <c r="C17" s="38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:E7"/>
@@ -4431,6 +4485,13 @@
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4453,17 +4514,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="79" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="79"/>
+      <c r="A1" s="95" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="95"/>
       <c r="C1" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="80" t="s">
-        <v>153</v>
-      </c>
-      <c r="E1" s="81"/>
+      <c r="D1" s="96" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="12"/>
@@ -4473,19 +4534,19 @@
       <c r="E2" s="16"/>
     </row>
     <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="77" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="77"/>
+      <c r="A3" s="88" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="88"/>
       <c r="C3" s="18"/>
-      <c r="D3" s="77" t="s">
+      <c r="D3" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
     </row>
     <row r="4" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="16"/>
@@ -4495,49 +4556,49 @@
       <c r="E4" s="16"/>
     </row>
     <row r="5" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="76" t="s">
+      <c r="B5" s="86"/>
+      <c r="C5" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="87"/>
     </row>
     <row r="6" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="69" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="76" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
+      <c r="A6" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="86"/>
+      <c r="C6" s="87" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
     </row>
     <row r="7" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="69" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="69"/>
-      <c r="C7" s="70" t="s">
+      <c r="A7" s="86" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="86"/>
+      <c r="C7" s="90" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="90"/>
     </row>
     <row r="8" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="69"/>
-      <c r="B8" s="69"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
+      <c r="A8" s="86"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="90"/>
+      <c r="D8" s="90"/>
+      <c r="E8" s="90"/>
     </row>
     <row r="9" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="18"/>
@@ -4547,17 +4608,17 @@
       <c r="E9" s="18"/>
     </row>
     <row r="10" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="78"/>
-      <c r="C10" s="78"/>
-      <c r="D10" s="78"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
       <c r="E10" s="18"/>
     </row>
     <row r="11" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="A11" s="78"/>
-      <c r="B11" s="78"/>
+      <c r="A11" s="98"/>
+      <c r="B11" s="98"/>
       <c r="C11" s="20" t="s">
         <v>30</v>
       </c>
@@ -4565,86 +4626,97 @@
         <v>31</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.4">
-      <c r="A12" s="76" t="s">
+      <c r="A12" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="76"/>
+      <c r="B12" s="87"/>
       <c r="C12" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.4">
+      <c r="A13" s="87" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="87"/>
+      <c r="C13" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="16" x14ac:dyDescent="0.4">
+      <c r="A14" s="87" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="87"/>
+      <c r="C14" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="37" t="s">
+      <c r="D14" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="39" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.4">
-      <c r="A13" s="76" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="76"/>
-      <c r="C13" s="37" t="s">
+      <c r="E14" s="18" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.4">
+      <c r="A15" s="88" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="88"/>
+      <c r="C15" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="37" t="s">
+      <c r="D15" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="39" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="16" x14ac:dyDescent="0.4">
-      <c r="A14" s="76" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="76"/>
-      <c r="C14" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.4">
-      <c r="A15" s="77" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="77"/>
-      <c r="C15" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>72</v>
-      </c>
       <c r="E15" s="41" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="16" x14ac:dyDescent="0.4">
-      <c r="A16" s="70" t="s">
+      <c r="A16" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="70"/>
+      <c r="B16" s="90"/>
       <c r="C16" s="39" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:E6"/>
@@ -4653,17 +4725,6 @@
     <mergeCell ref="C5:J5"/>
     <mergeCell ref="D3:I3"/>
     <mergeCell ref="D1:E1"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4686,7 +4747,7 @@
         <v>50</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
@@ -4718,22 +4779,22 @@
         <v>40</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="17" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="84"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="103"/>
       <c r="F4" s="29"/>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
@@ -4743,223 +4804,213 @@
       <c r="A5" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="57" t="s">
-        <v>130</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
+      <c r="B5" s="73" t="s">
+        <v>217</v>
+      </c>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
     </row>
     <row r="6" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="57" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
+      <c r="B6" s="73" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
     </row>
     <row r="7" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="58"/>
-      <c r="B7" s="58" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
+      <c r="A7" s="74"/>
+      <c r="B7" s="74" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
     </row>
     <row r="8" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
     </row>
     <row r="9" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="27">
         <v>1</v>
       </c>
-      <c r="B9" s="85" t="s">
-        <v>133</v>
-      </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
+      <c r="B9" s="104" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" s="74"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
     </row>
     <row r="10" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="27">
         <v>2</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
     </row>
     <row r="11" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="58" t="s">
+      <c r="A11" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
     </row>
     <row r="12" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="27">
         <v>1</v>
       </c>
-      <c r="B12" s="57" t="s">
-        <v>135</v>
-      </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
+      <c r="B12" s="73" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
     </row>
     <row r="13" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="27">
         <v>2</v>
       </c>
-      <c r="B13" s="57" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
+      <c r="B13" s="73" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
     </row>
     <row r="14" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="27">
         <v>3</v>
       </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
     </row>
     <row r="15" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="27">
         <v>4</v>
       </c>
-      <c r="B15" s="58"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
     </row>
     <row r="16" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="27">
         <v>5</v>
       </c>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
     </row>
     <row r="17" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="58" t="s">
+      <c r="A17" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
     </row>
     <row r="18" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="57" t="s">
+      <c r="A18" s="73" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" s="74"/>
+      <c r="C18" s="74"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+    </row>
+    <row r="19" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="73" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" s="74"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+    </row>
+    <row r="20" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" s="99"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="100"/>
+    </row>
+    <row r="21" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="74"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="74"/>
+    </row>
+    <row r="22" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="73" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="73"/>
+      <c r="C22" s="73"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+    </row>
+    <row r="23" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="75" t="s">
         <v>137</v>
       </c>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-    </row>
-    <row r="19" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="57" t="s">
+      <c r="B23" s="99"/>
+      <c r="C23" s="99"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="100"/>
+    </row>
+    <row r="24" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="73" t="s">
         <v>138</v>
       </c>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-    </row>
-    <row r="20" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="B20" s="86"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="87"/>
-    </row>
-    <row r="21" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="58" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-    </row>
-    <row r="22" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="57" t="s">
-        <v>140</v>
-      </c>
-      <c r="B22" s="57"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
-    </row>
-    <row r="23" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="60" t="s">
-        <v>141</v>
-      </c>
-      <c r="B23" s="86"/>
-      <c r="C23" s="86"/>
-      <c r="D23" s="86"/>
-      <c r="E23" s="87"/>
-    </row>
-    <row r="24" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="57" t="s">
-        <v>142</v>
-      </c>
-      <c r="B24" s="58"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
     </row>
     <row r="25" spans="1:5" s="17" customFormat="1" ht="292.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="74"/>
     </row>
     <row r="26" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="58" t="s">
+      <c r="A26" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="74"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
     </row>
     <row r="27" spans="1:5" s="17" customFormat="1" ht="14" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A23:E23"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
@@ -4974,6 +5025,16 @@
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A23:E23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B9" r:id="rId1" xr:uid="{C91E6952-1EA6-4A40-B517-F63B8F205E11}"/>
